--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99269</v>
+        <v>99380</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,11 +2486,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99380</v>
+        <v>99385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99385</v>
+        <v>99387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99387</v>
+        <v>99393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99393</v>
+        <v>99405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99405</v>
+        <v>99406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99406</v>
+        <v>99409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 20366-2024 artfynd.xlsx
+++ b/artfynd/A 20366-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
         <v>135474345</v>
       </c>
       <c r="B17" t="n">
-        <v>99409</v>
+        <v>99413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
